--- a/experimental/attention/kv_cache_turbo_quant/task_submission/2.1 精度自验证报告.xlsx
+++ b/experimental/attention/kv_cache_turbo_quant/task_submission/2.1 精度自验证报告.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1 用例参数" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2 精度对比结果" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3 截图" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="附表 生态标准判定" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 用例参数" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 精度对比结果" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 截图" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附表 生态标准判定" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,7 +87,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -168,7 +167,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -176,20 +175,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="2981325"/>
+    <ext cx="9525000" cy="3971925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -198,23 +197,23 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="2914650"/>
+    <ext cx="9525000" cy="19088100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -223,23 +222,148 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>127</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="4019550"/>
+    <ext cx="8753475" cy="10382250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>184</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="10668000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>243</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8439150" cy="4191000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>268</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="2933700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>286</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="23336250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>411</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="17249775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -536,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -557,98 +681,57 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>算子：aclnnKvCacheTurboQuant（TurboQuant 在线 KV cache 量化 encode）　硬件：Atlas 800T A2（910B3）　CANN：9.1.0　精度标杆：任务包 golden.py　用例定义：任务包 case.json</t>
+          <t>算子：aclnnKvCacheTurboQuant（TurboQuant 在线 KV cache 量化 encode）　硬件：Atlas 800T A2（910B3）　精度标杆：任务包 golden.py（只读）　用例定义：任务包 case.json（只读）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>本轮环境：Atlas 800T A2（910B3）×1　CANN：9.1.0　torch 2.7.1 / torch_npu 2.7.1.post4　Python：3.11.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>num_tokens</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>num_kv_heads</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>head_dim</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>mse_bits</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>gqa_decode_b1</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>GQA decode</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>gqa_decode_b64</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>GQA decode batch</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>gqa_prefill_t2048</t>
+          <t>gqa_decode_b1</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2048</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>8</v>
@@ -661,18 +744,18 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>GQA prefill</t>
+          <t>GQA decode（rows=8）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>gqa_mse2_t2048</t>
+          <t>gqa_decode_b64</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2048</v>
+        <v>64</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>8</v>
@@ -681,18 +764,18 @@
         <v>128</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2-bit 主编码 + 1-bit QJL</t>
+          <t>GQA decode（rows=512）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>gqa_mse4_t2048</t>
+          <t>gqa_prefill_t2048</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -705,25 +788,82 @@
         <v>128</v>
       </c>
       <c r="E9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>GQA prefill（rows=16384）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>gqa_mse2_t2048</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>2048</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>2-bit 主编码 + 1-bit QJL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>gqa_mse4_t2048</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>2048</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>4-bit 主编码 + 1-bit QJL</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>输入数据：kv_vectors（bf16，(num_tokens·num_kv_heads, 128)）、rotation_matrix / qjl_matrix（fp32，[128,128]），固定 seed 生成；对拍读数与 golden.py 使用同一份数据文件。</t>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>输入数据：由任务包 generate_data.py（master_seed 20260928）生成，**每个 case 一份**：kv_vectors（bf16，(num_tokens·num_kv_heads,128)）、ip_query（bf16，内积口径用，与 x 相关）、rotation_matrix / qjl_matrix（fp32[128,128]，官方共享件）；各文件 sha256 逐行记在 2.2 日志正文（input= / ip_query= 行）。对拍读数与 golden.py 使用同一份数据文件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>原始记录：docs/evidence/repro/2026-09-30_kctq_bitexact_reverse/（delivery/runall_final.log 为本报告唯一数据源）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A11:G11"/>
+  <mergeCells count="4">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -735,14 +875,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -895,6 +1036,11 @@
           <t>quant_gamma</t>
         </is>
       </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -922,6 +1068,11 @@
           <t>0/8</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>逐位一致</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -949,6 +1100,11 @@
           <t>0/512</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>逐位一致</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -973,7 +1129,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1/16384</t>
+          <t>0/16384</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>逐位一致</t>
         </is>
       </c>
     </row>
@@ -1003,6 +1164,11 @@
           <t>0/16384</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>逐位一致</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1017,7 +1183,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>1/262144</t>
+          <t>0/262144</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1030,303 +1196,435 @@
           <t>0/16384</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>逐位一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>本行为诊断口径（逐字节完全相等），严于官方精度标准 —— 《生态算子开源精度标准》§0 声明不覆盖整型/位打包类输出。本轮 5 个 case 的 4 路输出全部 0 不一致（bit-exact），即 quant_norm / quant_gamma 的 bf16 输出与 golden.py 逐位相同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2.2b 逐位一致的强化验证（独立于上表的补充实验）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>记录（docs/evidence/repro/2026-09-30_kctq_bitexact_reverse/）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>5 用例 × mse_bits∈{2,3,4} 交叉矩阵</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>15 组（5 输入 × 3 档位）</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>15/15 组四输出逐位一致</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>cross_matrix_15.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>fp32 行范数中间量 vs NPU torch.linalg.vector_norm</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>16384 行</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0/16384 不一致（逐位）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>verify_fp32_norm.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>边界用例套件（tokens=1 档 / 边界 shape / 极值输入）</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>10 例</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>10/10 对拍 PASS</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>regression_edge_cases.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>非法输入拒绝套件</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>11 例非法 + 1 例合法基准</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>11/11 拒绝，合法基准接受</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>regression_invalid_cases.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>算子 UT（--ophost）</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2 suites / 24 tests</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>24/24 PASSED</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>regression_ut.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>2.3 相对 MSE（任务书 §3.2：MSE / ‖x‖² &lt; 0.05）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>case (mse_bits)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>实测（MSE-only 重构）</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>对照（重构＋QJL 项）</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>实测（主量化＋QJL 完整重构）</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>对照（仅主量化，不判定）</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>阈值</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>判定（按实测列）</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>gqa_decode_b1 (3)</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>0.1358</v>
-      </c>
-      <c r="D18" s="4" t="n">
+      <c r="B27" s="4" t="n">
+        <v>0.014143</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0.039306</v>
+      </c>
+      <c r="D27" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>gqa_decode_b64 (3)</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>0.0345</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>0.1253</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>gqa_prefill_t2048 (3)</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>0.0342</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>0.1228</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>gqa_mse2_t2048 (2)</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>0.1166</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>0.4182</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>超出</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>gqa_mse4_t2048 (4)</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>0.0094</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>0.0336</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>备注：gqa_mse2_t2048（mse_bits=2）实测 0.1166 超出 0.05；该档取值由 case.json 指定，其《调研分析报告》§5 参考值为 0.1159。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>2.4 内积估计误差（任务书 §3.2：|&lt;q,x̂&gt;−&lt;q,x&gt;| / |&lt;q,x&gt;| 的 95th percentile &lt; 0.1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>case (mse_bits)</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>实测（分母 |&lt;q,x&gt;|，任务书字面式）</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>阈值</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>判定（按实测列）</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>参照（分母 ‖q‖·‖x‖）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>gqa_decode_b1 (3)</t>
+          <t>gqa_decode_b64 (3)</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>0.462</v>
+        <v>0.012241</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>超出</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0.0397</v>
+        <v>0.033947</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>gqa_decode_b64 (3)</t>
+          <t>gqa_prefill_t2048 (3)</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>5.6457</v>
+        <v>0.012274</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>超出</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0.0606</v>
+        <v>0.033966</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>gqa_prefill_t2048 (3)</t>
+          <t>gqa_mse2_t2048 (2)</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>4.3354</v>
+        <v>0.041852</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>超出</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>0.0624</v>
+        <v>0.11601</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>gqa_mse4_t2048 (4)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>0.003365</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0.009313999999999999</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>口径：官方 2026-09-28 答复明确「反量化 = 主量化 + 1-bit QJL 残差完整重构」，即 x̂ = (‖x‖·centroid[idx] + γ·sqrt(pi/2)/d·(sign@S)) @ H。对照列（仅主量化）不含 QJL：2-bit 实测约 0.116，正是 2-bit 标量量化的理论下界（Lloyd-Max），故 2-bit 的 0.05 目标需按完整重构路径评估 —— 实测 0.0419 通过。另：官方为 2-bit 单列逐向量阈值（max&lt;0.10、P95&lt;0.06），实测 0.0761 / 0.0535 通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>2.4 内积估计误差（任务书 §3.2：|&lt;q,x̂&gt;−&lt;q,x&gt;| / |&lt;q,x&gt;| 的 95th percentile &lt; 0.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>case (mse_bits)</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>实测（分母 max(|&lt;q,x&gt;|,1e-6)，任务书字面式）</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>阈值</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>gqa_decode_b1 (3)</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>0.032324</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>gqa_decode_b64 (3)</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>0.033372</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>gqa_prefill_t2048 (3)</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>0.032896</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>gqa_mse2_t2048 (2)</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>7.6678</v>
-      </c>
-      <c r="C31" s="4" t="n">
+      <c r="B40" s="4" t="n">
+        <v>0.07556499999999999</v>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>超出</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>0.1124</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>gqa_mse4_t2048 (4)</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>2.1788</v>
-      </c>
-      <c r="C32" s="4" t="n">
+      <c r="B41" s="4" t="n">
+        <v>0.015293</v>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>超出</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0.031</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>两列均为同一实测误差量、不同归一化的 95th percentile；&lt;q,x&gt; 为随机向量对，|&lt;q,x&gt;| 随 q、x 近正交而趋小，该列取值由采样集决定。</t>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>q 取官方件 ip_query（与 x 相关：q = BF16(BF16(x)+0.5·N(0,1))），统计范围为全部 token×head 向量。任务书字面分母 |&lt;q,x&gt;| 在 q 与 x 相关时非病态，5/5 case 均 &lt; 0.1。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A33:E33"/>
+  <mergeCells count="3">
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A42:E42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1338,27 +1636,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>截图 1：与 golden.py 逐位对拍（gqa_prefill_t2048, bits=3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>截图 2：V3 指标（相对 MSE / 内积 p95，gqa_prefill_t2048, bits=3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>截图 3：边界用例套件（10 例）对拍结果</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>00 环境（NPU / CANN 版本 / Python 栈 / 关键环境变量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>01 一键自测总览（5 case：V1 契约 → V2 逐字节对拍 → V3 指标 → 生态标准层 → 计时）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>02 逐字节对拍（V1 契约 + V2 与 golden.py 位级一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>03 V3 精度指标（任务书 §3.2 字面口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>04 生态标准层（《生态算子开源精度标准》混合容差）</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>05 构建与算子 UT（tiling 17 + infershape 7 = 24/24）</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>06 性能采样（三轮，warmup=3 / repeat=10 取中位数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>07 边界用例套件</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>标准依据：ops-transformer/third_party/opbase/docs/zh/ops_precision_standard/experimental_standard.md（§0 声明不覆盖整型/位打包类输出；§2.2 为 BFLOAT16 行判据）</t>
+          <t>标准依据：ops-transformer/third_party/opbase/docs/zh/ops_precision_standard/experimental_standard.md（§0 声明不覆盖整型/位打包类输出；§2.2 为 BFLOAT16 行判据）；本表数值由 2.2 日志的 [STD] 段落解析生成。</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1780,12 @@
           <t>1.00000000 / 0</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>0/384</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>0/128</t>
         </is>
@@ -1479,12 +1812,12 @@
           <t>1.00000000 / 0</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>0/24576</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>0/8192</t>
         </is>
@@ -1508,15 +1841,15 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>1.00000000 / 0.015625</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+          <t>1.00000000 / 0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>0/786432</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>0/262144</t>
         </is>
@@ -1543,12 +1876,12 @@
           <t>1.00000000 / 0</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>0/524288</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>0/262144</t>
         </is>
@@ -1575,14 +1908,14 @@
           <t>1.00000000 / 0</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>0/1048576</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>1/262144（匹配率 0.99999619）</t>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0/262144</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">

--- a/experimental/attention/kv_cache_turbo_quant/task_submission/2.1 精度自验证报告.xlsx
+++ b/experimental/attention/kv_cache_turbo_quant/task_submission/2.1 精度自验证报告.xlsx
@@ -200,7 +200,7 @@
       <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9525000" cy="19088100"/>
+    <ext cx="9382125" cy="1962150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -222,10 +222,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8753475" cy="10382250"/>
+    <ext cx="8334375" cy="723900"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -247,10 +247,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>184</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9525000" cy="10668000"/>
+    <ext cx="9525000" cy="12954000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -272,10 +272,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>243</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8439150" cy="4191000"/>
+    <ext cx="8439150" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -297,7 +297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>268</row>
+      <row>126</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525000" cy="2933700"/>
@@ -322,10 +322,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>286</row>
+      <row>144</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9525000" cy="23336250"/>
+    <ext cx="9525000" cy="1943100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -347,7 +347,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>411</row>
+      <row>157</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525000" cy="17249775"/>
@@ -1636,7 +1636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A411"/>
+  <dimension ref="A1:A157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,43 +1653,43 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>02 逐字节对拍（V1 契约 + V2 与 golden.py 位级一致）</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>03 V3 精度指标（任务书 §3.2 字面口径）</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="1" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
         <is>
           <t>04 生态标准层（《生态算子开源精度标准》混合容差）</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="1" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
         <is>
           <t>05 构建与算子 UT（tiling 17 + infershape 7 = 24/24）</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="1" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
         <is>
           <t>06 性能采样（三轮，warmup=3 / repeat=10 取中位数）</t>
         </is>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" s="1" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
         <is>
           <t>07 边界用例套件</t>
         </is>
